--- a/payroll/2026/excel/20260912-0913.xlsx
+++ b/payroll/2026/excel/20260912-0913.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lubq\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\personal\cqsj\payroll\2026\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935330BB-81F7-4F24-AA17-39828A30F6C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E751D45F-1CA6-4CC0-A07C-7D8AD71D8F40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10035" yWindow="330" windowWidth="27975" windowHeight="19845" activeTab="1" xr2:uid="{7A907552-1C41-4484-ABB7-89D0B7E40110}"/>
+    <workbookView xWindow="17010" yWindow="345" windowWidth="27975" windowHeight="19845" activeTab="1" xr2:uid="{7A907552-1C41-4484-ABB7-89D0B7E40110}"/>
   </bookViews>
   <sheets>
     <sheet name="产出" sheetId="1" r:id="rId1"/>
@@ -1164,7 +1164,7 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1201,37 +1201,7 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2372,7 +2342,7 @@
       </c>
       <c r="C24" s="14">
         <f t="shared" si="0"/>
-        <v>385</v>
+        <v>71</v>
       </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
@@ -2380,9 +2350,7 @@
         <v>41</v>
       </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14">
-        <v>314</v>
-      </c>
+      <c r="H24" s="14"/>
       <c r="I24" s="14">
         <v>30</v>
       </c>
@@ -2397,7 +2365,7 @@
       </c>
       <c r="C25" s="14">
         <f t="shared" si="0"/>
-        <v>169</v>
+        <v>483</v>
       </c>
       <c r="D25" s="14"/>
       <c r="E25" s="14"/>
@@ -2407,7 +2375,9 @@
       <c r="G25" s="14">
         <v>53</v>
       </c>
-      <c r="H25" s="14"/>
+      <c r="H25" s="14">
+        <v>314</v>
+      </c>
       <c r="I25" s="14">
         <v>30</v>
       </c>
@@ -2733,12 +2703,12 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B39:B1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
